--- a/experiment2/data_processing/exp_data/08_ranova_input.xlsx
+++ b/experiment2/data_processing/exp_data/08_ranova_input.xlsx
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>634.3200000000001</v>
+        <v>594.2727272727273</v>
       </c>
     </row>
     <row r="12">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>558.8461538461538</v>
+        <v>704.5263157894736</v>
       </c>
     </row>
     <row r="22">
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>681.8571428571429</v>
+        <v>640.7368421052631</v>
       </c>
     </row>
     <row r="24">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>737.5384615384615</v>
+        <v>719.4</v>
       </c>
     </row>
     <row r="25">
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>507.4074074074074</v>
+        <v>513.5384615384615</v>
       </c>
     </row>
     <row r="28">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>676.1538461538462</v>
+        <v>660.36</v>
       </c>
     </row>
     <row r="34">
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>682.0769230769231</v>
+        <v>670.28</v>
       </c>
     </row>
     <row r="37">
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>452.1</v>
+        <v>441.3157894736842</v>
       </c>
     </row>
     <row r="62">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>714.3333333333334</v>
+        <v>698.4615384615385</v>
       </c>
     </row>
     <row r="63">
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>697.5769230769231</v>
+        <v>664.7916666666666</v>
       </c>
     </row>
     <row r="65">
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>644.8076923076923</v>
+        <v>628.84</v>
       </c>
     </row>
     <row r="112">
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>637.8148148148148</v>
+        <v>622.3076923076923</v>
       </c>
     </row>
     <row r="113">
@@ -2506,7 +2506,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>384.1428571428572</v>
+        <v>380.1481481481482</v>
       </c>
     </row>
     <row r="117">
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>597.88</v>
+        <v>581.6666666666666</v>
       </c>
     </row>
     <row r="130">
@@ -5711,7 +5711,7 @@
         <v>563.2222222222222</v>
       </c>
       <c r="E3" t="n">
-        <v>634.3200000000001</v>
+        <v>594.2727272727273</v>
       </c>
       <c r="F3" t="n">
         <v>703.2</v>
@@ -5751,16 +5751,16 @@
         <v>575.6206896551724</v>
       </c>
       <c r="C5" t="n">
-        <v>558.8461538461538</v>
+        <v>704.5263157894736</v>
       </c>
       <c r="D5" t="n">
         <v>668.125</v>
       </c>
       <c r="E5" t="n">
-        <v>681.8571428571429</v>
+        <v>640.7368421052631</v>
       </c>
       <c r="F5" t="n">
-        <v>737.5384615384615</v>
+        <v>719.4</v>
       </c>
       <c r="G5" t="n">
         <v>564.4615384615385</v>
@@ -5774,7 +5774,7 @@
         <v>463.2307692307692</v>
       </c>
       <c r="C6" t="n">
-        <v>507.4074074074074</v>
+        <v>513.5384615384615</v>
       </c>
       <c r="D6" t="n">
         <v>472.2916666666667</v>
@@ -5797,7 +5797,7 @@
         <v>631</v>
       </c>
       <c r="C7" t="n">
-        <v>676.1538461538462</v>
+        <v>660.36</v>
       </c>
       <c r="D7" t="n">
         <v>708.6896551724138</v>
@@ -5806,7 +5806,7 @@
         <v>766.483870967742</v>
       </c>
       <c r="F7" t="n">
-        <v>682.0769230769231</v>
+        <v>670.28</v>
       </c>
       <c r="G7" t="n">
         <v>635.9230769230769</v>
@@ -5901,7 +5901,7 @@
         <v>476.64</v>
       </c>
       <c r="G11" t="n">
-        <v>452.1</v>
+        <v>441.3157894736842</v>
       </c>
     </row>
     <row r="12">
@@ -5909,13 +5909,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="n">
-        <v>714.3333333333334</v>
+        <v>698.4615384615385</v>
       </c>
       <c r="C12" t="n">
         <v>620.84</v>
       </c>
       <c r="D12" t="n">
-        <v>697.5769230769231</v>
+        <v>664.7916666666666</v>
       </c>
       <c r="E12" t="n">
         <v>698.1481481481482</v>
@@ -6096,10 +6096,10 @@
         <v>602.2857142857143</v>
       </c>
       <c r="C20" t="n">
-        <v>644.8076923076923</v>
+        <v>628.84</v>
       </c>
       <c r="D20" t="n">
-        <v>637.8148148148148</v>
+        <v>622.3076923076923</v>
       </c>
       <c r="E20" t="n">
         <v>614.16</v>
@@ -6116,7 +6116,7 @@
         <v>26</v>
       </c>
       <c r="B21" t="n">
-        <v>384.1428571428572</v>
+        <v>380.1481481481482</v>
       </c>
       <c r="C21" t="n">
         <v>439.4444444444445</v>
@@ -6165,7 +6165,7 @@
         <v>519.59375</v>
       </c>
       <c r="C23" t="n">
-        <v>597.88</v>
+        <v>581.6666666666666</v>
       </c>
       <c r="D23" t="n">
         <v>542.76</v>
